--- a/data/processed/case_database_v0.1.xlsx
+++ b/data/processed/case_database_v0.1.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29400" windowHeight="14040" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Case Database" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,182 +16,27 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Database'!$A$1:$X$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evidence Index'!$A$1:$F$27</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="2">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -199,204 +45,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E5E4E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="002E5E4E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -406,334 +64,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1086,6 +450,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1096,7 +461,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -1118,2198 +483,2199 @@
     <col width="38" customWidth="1" min="18" max="18"/>
     <col width="36" customWidth="1" min="19" max="19"/>
     <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="22"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
     <col width="34" customWidth="1" min="23" max="23"/>
     <col width="44" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>case_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>case_type</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>initial_production_layout</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>initial_main_markets</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>initial_supply_chain</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>initial_problem</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>decision_trigger</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>trigger_detail</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>decision_type</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>actual_decision</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>related_risk</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>outcome_cost_impact</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>outcome_production_performance</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>outcome_market_access</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>outcome_supply_chain_impact</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>outcome_verdict</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>related_evidence_ids</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>verification_status</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="68" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RELOC_001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>比亚迪 BYD</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Automotive (EV)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>东方财富网（转比亚迪官方）</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2024-07-04</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>整车与电池产能全部位于中国（深圳、西安、长沙、常州等基地），海外无自有乘用车整车产能。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>中国市场为主，出口快速扩张至东南亚、欧洲、拉美、澳新。</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>电池、电机、电控垂直整合，供应链集中于中国境内。</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>纯出口模式在东盟右舵市场面临整车进口税与本地化要求；美国、欧盟对华电动车关税与反补贴调查抬升出口成本。</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>美国对华电动车加征关税、欧盟反补贴调查，出口关税壁垒上升；泰国对本地组装提供 BOI 优惠。</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年产能约 15 万辆，投资约 350 亿泰铢（约 69.5 亿元人民币）。中国产能保留并继续扩产。</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Market Access Risk</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>本地化生产规避东盟整车进口税，叠加泰国 BOI 税收优惠降低综合税负；但泰国本地零部件配套不足，短期单位成本高于中国。</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>开工到投产仅 16 个月，创中国车企在泰最快投产纪录；第 800 万辆新能源汽车在泰国工厂下线。</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>直接覆盖泰国及东盟右舵市场，从整车出口转为本地供应，显著降低准入壁垒。</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>关键零部件初期仍依赖中国进口，本地供应链配套率低，形成新的跨境物流依赖。</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>成功（本地供应链仍依赖中国）</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>高（官方发布 + 多家主流媒体一致）</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>整车厂跟随关税出海的标准案例，可作为 Scenario Simulation 的基准情景。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="51" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RELOC_002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>长安汽车 Changan Automobile</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Automotive (EV)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>易车 / 证券之星（投资者互动平台）</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>https://news.yiche.com/hao/wenzhang/100585175/</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>整车产能集中于中国（重庆、合肥、南京等），海外以整车出口为主。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>中国为主，海外处于快速扩张期（2024 年海外销售 53.6 万辆）。</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>整车与三电系统主要在中国生产，海外仅有散件组装。</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>东南亚右舵市场准入依赖整车出口，关税与local content要求抬升成本。</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>market_access</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Market Access Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>获得泰国 BOI 优惠与 EV3.5 补贴资格，降低进入东盟的单位成本。</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>2026-09 公司确认罗勇工厂已建成投产并具备整车本地化生产能力。</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>从整车出口转为本地生产，满足泰国本地化要求，保住补贴资格。</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>零部件本地化配套率仍在爬坡，初期依赖中泰跨境供应。</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>成功（早期，产能爬坡中）</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>高（公司互动平台确认 + 媒体报道）</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>与比亚迪泰国案例对照，可用于比较不同车企的东南亚本地化路径。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>RELOC_003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>国轩高科 Gotion High-Tech</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>EV Battery</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2022-11-19</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>中国动力电池市场为主，海外客户（大众等）快速增加。</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>market_access</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>越南 VinFast 本地化生产需要就近电池配套，越南对电池进口设有本地化要求。</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>与 Vingroup 旗下 VinES 合资（国轩 51% / VinES 49%）在越南河静经济开发区建越南首座 LFP 电池工厂，一期规划年产能 5GWh；2026-07 公司披露德国、越南、印尼、泰国四大海外基地已陆续投产，越南基地为亚洲首条 LFP 电芯工厂。</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk; Market Access Risk</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>就近配套降低物流与关税成本；越南人工与土地成本低于中国。</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>四大海外基地陆续投产，越南基地定位为亚洲首个 LFP 电芯工厂。</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>绑定 VinFast 这一本地整车客户，进入越南及东盟供货体系。</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>正负极等关键材料仍从中国输入，越南基地形成'中国材料—越南电芯'的跨境结构。</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>成功（材料端仍依赖中国）</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>中高（开工有明确报道；2026 年投产状态来自公司互动平台转述）</t>
         </is>
       </c>
-      <c r="X4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RELOC_004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>亿纬锂能 EVE Energy</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EV Battery / Energy Storage</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>新浪财经</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>锂电产能集中于中国（惠州、荆门、成都等），海外无大型自有厂房。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>中国为主，海外储能与圆柱电池客户（含特斯拉供应链）增长快。</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>材料与设备主要来自中国，产品以出口方式交付海外客户。</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>出口至欧美面临关税与供应链本地化要求，交付半径长、响应慢。</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>马来西亚产能提升出口业务规避税率的能力，降低对美出口关税成本。</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>二期投产形成规模化圆柱电池产能，海外交付能力显著提升。</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>马来西亚基地作为面向欧美客户的出口枢纽，缓解关税与本地化压力。</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>设备与材料初期仍由中国输入，形成'中国材料—马来西亚制造—欧美市场'链条。</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>成功（爬坡中）</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="W5" s="5" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>高（公司发布 + 主流财经媒体）</t>
         </is>
       </c>
-      <c r="X5" s="5" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>可用于比较'东南亚出口枢纽'与'近岸（墨西哥/匈牙利）'两种路径。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>RELOC_005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>欣旺达 Sunwoda</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>EV Battery / Consumer Battery</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>消费类与动力电池产能集中于中国（深圳、惠州、南京等）。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>中国为主，消费类电池出口欧美客户占比高。</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>电芯与材料主要来自中国，产品以整包出口。</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>消费电子客户要求供应商在东南亚备产能以分散关税与地缘风险。</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>美国对华加征关税及客户'中国+1'采购要求，推动消费类电芯产线外移。</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威消费类锂电池工厂项目，投资总额不超过 20 亿元人民币；2026-08 公司表示越南消费类电芯生产基地预计 2026 年底投产。中国产能保留。</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>越南基地降低对美出口关税暴露，但前期资本开支与本地配套成本较高。</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>截至 2026-08 仍在建设期，预计 2026 年底投产（结果尚待验证）。</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>满足欧美消费电子客户对非中国产能的采购要求。</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>材料仍由中国供应，越南以电芯制造环节为主。</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>待观察（尚未投产）</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="W6" s="5" t="inlineStr">
-        <is>
-          <t>中高（公告明确；投产时间来自公司投资者关系记录转述，NEWS_007 链接待补）</t>
-        </is>
-      </c>
-      <c r="X6" s="5" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>中高（公告明确；投产时间来自公司投资者关系记录转述）</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>少见的'结果尚未发生'案例，可用于测试模型对不确定结论的处理。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>RELOC_006</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>蜂巢能源 SVOLT</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>EV Battery</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>澎湃新闻</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2024-02-28</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>电芯与 PACK 产能集中于中国（常州、金坛、上饶等）。</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>中国整车客户为主，海外客户极少。</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>材料与设备全部来自中国。</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>中国客户（长城、合众/哪吒）在泰国建厂后需要本地电池配套；泰国对电池进口有关税。</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>market_access</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>跟随中国整车客户出海，满足泰国本地化电池配套要求。</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Market Access Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2024-02 投产并批量交付，产能按订单爬坡。</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>绑定泰国本地中国品牌整车客户，进入泰国本地供应体系。</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>电芯/材料仍从中国输入，泰国仅承担模组与 PACK 环节。</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>成功（局部环节外移）</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>高（多家媒体一致）</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>与 RETURN_004（蜂巢停建德国工厂）同一公司，可直接对比'东南亚收缩 vs 欧洲退出'的策略差异。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="84" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RELOC_007</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>华友钴业 Huayou Cobalt</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Battery Materials</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>新浪财经</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>钴/镍冶炼与前驱体产能集中于中国（浙江桐乡等），印尼仅有勘探布局。</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>中国正极与前驱体厂商为主。</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>镍钴原料高度依赖进口（刚果金钴、印尼镍矿），加工环节在中国。</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>上游镍资源受制于人，原料价格与供应稳定性风险高；印尼禁止原矿出口，倒逼本地冶炼。</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>supplier_issue</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>印尼 2020 年起禁止镍原矿出口，要求就地冶炼；下游电池需求推升镍资源安全诉求。</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>自 2018 年起在印尼布局镍钴资源，依托青山系莫罗瓦利与纬达贝工业园建设红土镍矿湿法冶炼项目（华越 6 万吨、华飞 12 万吨镍金属量等），2024-04 年产 12 万吨镍钴湿法项目达产；2026-01 表示 Pomalaa 年产 12 万吨镍金属量湿法项目预计 2026 年底建成投产。中国冶炼与材料产能保留。</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>印尼湿法冶炼的万吨镍投资约为世界同类项目的三分之一，原料自给降低成本。</t>
         </is>
       </c>
-      <c r="R8" s="5" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>多个湿法项目达产，关键原料自供比例显著提升。</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>以印尼镍产品供应中国及全球前驱体客户，绕开原矿出口禁令。</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>形成'印尼资源—中国材料'的双向依赖，海外上游集中度上升带来新的地缘风险。</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>成功（上游外移，加工仍在国内）</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="W8" s="5" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>高（公司公告 + 主流财经媒体）</t>
         </is>
       </c>
-      <c r="X8" s="5" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>典型的'资源端外移而非制造端外移'案例。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RELOC_008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>中伟股份 CNGR Advanced Material</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Battery Materials</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>和讯网 / 网易</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>三元前驱体产能集中于中国（湖南、贵州等），原料端依赖进口。</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>中国正极材料厂与日韩电池客户。</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>镍钴原料外购，冶炼与加工均在中国，资源依赖进口。</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>原料依赖进口导致成本与供应稳定性风险，且印尼原矿出口禁令压缩传统采购路径。</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>supplier_issue</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>印尼原矿出口禁令 + 客户对低碳、可追溯镍的需求。</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>在印尼建设北莫罗瓦利、莫罗瓦利、纬达贝三大原料基地，2024-04 三基地已投产；2026-01 莫罗瓦利中青新能源二期全面投产（首炉冰镍产出），在建及建成资源粗炼端产能约 12.5 万金属吨。中国前驱体产能保留。</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>自供原料比例提升，降低外购镍价波动影响。</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>三基地投产、二期冰镍产线投料试产成功，产能持续释放。</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>以自产镍资源支撑中国及海外前驱体客户供货。</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>海外上游集中于印尼，单一国家集中度风险上升。</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>成功（上游外移）</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>高（公司披露 + 媒体报道）</t>
         </is>
       </c>
-      <c r="X9" s="5" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>与华友钴业对照，可用于'资源国集中度'风险讨论。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>PLUS1_001</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>宁德时代 CATL</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>EV Battery</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>每日经济新闻 / 搜狐网</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>China + 1 strategy</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>电芯产能集中于中国（宁德、溧阳、宜宾、肇庆等），海外原仅有德国埃尔福特工厂。</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>中国 + 欧洲整车厂（宝马、大众、奔驰、Stellantis 等）。</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>材料与设备高度依赖中国供应链，产品以出口与本地组装方式交付欧洲客户。</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>欧洲本地化率与电池法规（EU Battery Regulation）要求提升，纯出口面临关税、碳足迹与供应链审查。</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>regulation_change</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>欧盟电池法规与本地化含量要求，叠加欧洲整车客户对就近供货的需求。</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>在匈牙利德布勒森建设欧洲第二座电池工厂，投资约 73.4 亿欧元（匈牙利史上最大外资项目之一），规划总产能 100GWh；2022-08 宣布，2023 年夏季首座电芯厂房动工，2026-08 取得厂房使用许可，2026-09-22 启动试生产；德国工厂与中国基地继续运营。</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Supply Chain Risk; Regulatory Risk</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>欧洲本地生产规避电池进口关税并获得本地补贴，但欧洲能源与人工成本显著高于中国。</t>
         </is>
       </c>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2026-09 进入试生产阶段，尚未规模量产（结果待验证）。</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>就近供应奔驰等欧洲客户，满足欧盟本地化与合规要求。</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>正极、负极、电解液等仍需中国及亚洲供应，形成'中国材料—欧洲电芯'结构。</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>待观察（试生产中，投资周期长）</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="W10" s="5" t="inlineStr">
-        <is>
-          <t>中高（2026 年节点高质量来源；2022 年投资额来自媒体转述，NEWS_013 链接待补）</t>
-        </is>
-      </c>
-      <c r="X10" s="5" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>中高（2026 年节点高质量来源；2022 年投资额来自媒体转述）</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>'欧洲本地化'路径的代表案例，与东南亚路径形成对照。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>PLUS1_002</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>宁德时代 CATL</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>EV Battery</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>东方财富网（转界面新闻）</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>China + 1 strategy</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>中国电芯产能为主，印尼仅有镍资源相关投资。</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>中国 + 欧洲 + 东南亚。</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>镍钴原料部分来自印尼，材料加工与电芯制造在中国。</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>印尼要求矿产资源本地化加工并延伸至电池制造，单纯采购镍矿的模式不可持续；同时需要覆盖东南亚增长市场。</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>regulation_change</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>印尼'下游化'政策要求镍矿就地加工并延伸至电池产业链。</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>由子公司普勤时代（CBL）、印尼国有矿业公司 ANTAM 与印尼电池公司 IBC 组成联合体，2025-06-29 在西爪哇省卡拉旺产业新城动工建设'从镍矿开采—冶炼—前驱体—电池制造—回收'一体化项目，总投资近 60 亿美元，电池产能规划 15GWh，可满足约 25–30 万辆汽车需求；中国产能保留。</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Supply Chain Risk; Regulatory Risk</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>一体化布局降低原料与中间品跨境成本，但前期资本开支巨大。</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>2025-06 动工，处于建设期（结果待验证）。</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>进入印尼本地供应链并满足资源下游化要求，辐射东南亚市场。</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>把镍资源与电池制造绑定在印尼，减少对中国中间品运输的依赖，但新增单一国家集中度。</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>待观察（建设中）</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="W11" s="5" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>中高（公司发布 + 多家媒体，含彭博社转述）</t>
         </is>
       </c>
-      <c r="X11" s="5" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>可用于讨论'资源国要求本地化'这一触发因素。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>PLUS1_003</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>比亚迪 BYD</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Automotive (EV)</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>凤凰科技（转路透社）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2025-01-22</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>China + 1 strategy</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>整车产能集中在中国，海外首个工厂为泰国罗勇（2024-07 投产）。</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>中国 + 东南亚 + 欧洲 + 拉美。</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>电池与核心零部件由中国供应。</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>印尼是东南亚最大汽车市场，但整车进口关税高且要求本地化生产。</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>印尼对整车进口征收高关税并推行电动车本地化要求，2023-05 与印尼政府签署投资谅解备忘录。</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>在西爪哇省苏邦工业园区建设印尼工厂，总投资约 10 亿美元，规划年产能 15 万辆，计划 2025 年底前竣工；与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Market Access Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>本地生产规避印尼整车进口关税，获得电动车补贴资格。</t>
         </is>
       </c>
-      <c r="R12" s="5" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>截至 2025 年报道仍处于建设阶段，预计 2025 年底竣工（结果待验证）。</t>
         </is>
       </c>
-      <c r="S12" s="5" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>以本地生产进入印尼市场，直接与日系品牌竞争。</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>电池与关键零部件初期由中国供应，形成中印尼跨境供应链。</t>
         </is>
       </c>
-      <c r="U12" s="5" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>待观察（建设中）</t>
         </is>
       </c>
-      <c r="V12" s="5" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>NEWS_015</t>
         </is>
       </c>
-      <c r="W12" s="5" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>中（来源为路透社转述的公司高管表态，竣工情况需以最新公告核实）</t>
         </is>
       </c>
-      <c r="X12" s="5" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>与 RELOC_001 同属比亚迪，可对比同一企业不同市场的进入节奏。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PLUS1_004</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>晶科能源 JinkoSolar</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Solar Manufacturing</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>东方财富财富号</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>https://caifuhao.eastmoney.com/news/20260225153639217944650</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>China + 1 strategy</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>硅片—电池—组件一体化产能以中国为核心。</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>全球（中国、欧洲、美国、新兴市场）。</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>硅料、硅片主要在中国，组件通过海外基地与出口进入欧美。</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>美国对东南亚四国光伏产品的双反与反规避调查，使'中国—东南亚—美国'路径的关税优势不稳定（参见 Task 1 的 CASE_002/CASE_003）。</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>美国对东南亚光伏组件的双反/反规避认定，以及美国本土制造激励，要求产能进一步分散。</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>保持中国核心产能，同时在马来西亚（对美/欧核心出口枢纽）、越南（一体化产能）与美国本土布局成熟产能，形成'中国 + 东南亚 + 北美'的三地结构。</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Regulatory Risk; Market Access Risk</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>马来西亚基地不受本轮关税影响，成为对美欧出口枢纽；美国本土产能直接受益于关税保护。</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>多地产能并行，具体产能与利用率需以公司财报核实。</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>通过多地产能规避单一市场的关税与反规避风险。</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>硅片、电池等中间品仍在区域内跨境流动，东南亚基地对中国中间品存在依赖。</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>成功（多地产能分散风险）</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="W13" s="5" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>中（来源为财经自媒体对公开产能布局的整理，需以公司年报/官网核实）</t>
         </is>
       </c>
-      <c r="X13" s="5" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>与 Task 1 的光伏反规避证据（CASE_002/CASE_003/DOC_001）直接呼应，可用于跨任务串联。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="51" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PLUS1_005</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>三星电子 Samsung Electronics</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Electronics / Semiconductor</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>新浪财经 / 东方财富网</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>https://finance.sina.com.cn/stock/t/2026-05-27/doc-inhzikrs0845798.shtml</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>China + 1 strategy</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>半导体与消费电子产能分布在中国（西安 NAND、苏州封测）、韩国、越南（手机组装）。</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>全球。</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>关键零部件来自韩国、日本、中国，越南承担组装环节。</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>中美科技摩擦与关税使单一产地风险上升，越南被定位为分散地；同时 AI 需求推升存储芯片产能缺口。</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>geopolitical_uncertainty</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>中美科技与关税摩擦，以及 AI 驱动的存储芯片短缺，推动封装测试产能向第三国分散。</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>计划在越南北部（太原省）投资约 40 亿美元建设芯片测试与封装工厂，分阶段实施；中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>越南人工与土地成本低于韩国，但芯片封测对工程师与配套要求高，初期效率受限。</t>
         </is>
       </c>
-      <c r="R14" s="5" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>截至 2026 年仍为投资计划阶段（结果待验证）。</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>分散对单一国家出口管制的暴露。</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>封装测试外移，但前道晶圆制造仍集中在韩国与中国。</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>待观察（计划阶段）</t>
         </is>
       </c>
-      <c r="V14" s="5" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="W14" s="5" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>中（多方媒体转述，未见公司正式公告）</t>
         </is>
       </c>
-      <c r="X14" s="5" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>半导体行业'China+1'的代表，按任务优先级属第二梯队。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="51" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>RETURN_001</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Battery Materials</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Reconsideration / Return to China</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>中国 + 海外电池客户（含欧美）。</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>基膜与涂覆材料主要在中国生产，产品出口海外。</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>cost_change</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）。</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>2026-05-22 董事会审议通过《关于终止在马来西亚投资建设锂电池隔离膜项目的议案》，终止原计划约 20 亿元的马来西亚隔膜项目，资源回投国内，优化资源配置、降低风险。</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>避免在行业下行期投入 20 亿元海外资本开支，节省资金；但失去东南亚本地化产能抓手。</t>
         </is>
       </c>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>国内产能继续承担全球交付，海外扩张暂停。</t>
         </is>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>对海外客户仍以中国出口方式交付，关税暴露未消除。</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>海外供应链布局收缩，对单一中国基地的依赖上升。</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>主动止损（成功止损，但海外布局目标未达成）</t>
         </is>
       </c>
-      <c r="V15" s="5" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="W15" s="5" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>高（上市公司公告，多家财经媒体一致）</t>
         </is>
       </c>
-      <c r="X15" s="5" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>完整的'规划→终止'闭环案例，最能体现 Return/Reconsideration 类型。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="51" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>RETURN_002</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Electronics Manufacturing</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Reconsideration / Return to China</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>苹果产品组装以中国大陆为核心，印度、越南为分散地。</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>全球。</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>关键模组、设备与工程技术人员高度依赖中国大陆。</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>为分散地缘风险，苹果推动印度组装比例提升，但印度工厂良率、配套与工程能力不足，关键组件仍依赖进口。</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>geopolitical_uncertainty</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>印度本地化配套与技术能力不足，导致良率与交付不达预期。</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>2025 年 7 月及 12 月，富士康两度从印度工厂撤回中国大陆工程师与技术团队，部分产能与订单回流中国大陆；印度的组装布局并未取消，但节奏明显放缓。</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；中国基地继续承担高难度工序。</t>
         </is>
       </c>
-      <c r="R16" s="5" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>印度工厂良率与产能爬坡受阻，中国大陆产能利用率回升。</t>
         </is>
       </c>
-      <c r="S16" s="5" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>对美出口仍依托中国与东南亚双通道。</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>验证了'关键工序与工程能力仍在中国'的结构性依赖。</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>局部回流（未完全放弃印度）</t>
         </is>
       </c>
-      <c r="V16" s="5" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="W16" s="5" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>中高（多家媒体一致，均引自知情人士）</t>
         </is>
       </c>
-      <c r="X16" s="5" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>最好与'订单回流中国'行业案例（RETURN_003）一起用于情景模拟。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="68" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>RETURN_003</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>General Manufacturing / Supply Chain</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Reconsideration / Return to China</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>过去数年，为规避美国关税，大量企业把产能从中国迁往越南、印度、墨西哥等地，中国产能相应压缩。</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>以美国为主要出口市场。</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>从基础螺丝到核心模具、设备与工程人员仍依赖中国供应。</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>落地后出现'搬得出、难运转'：当地劳动力、供应商、设备、电力与物流成本高于预期，关税优势被成本吞噬；越南 2023 年及之后反复出现电力短缺导致工厂停产。</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>cost_change</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>东南亚等地综合成本高于预期 + 电力等基础设施不稳定，抵消关税收益。</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形成'中国为主 + 东南亚保留'的混合结构。</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Supply Chain Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>回流后综合成本下降，关税优势部分让位于运转效率。</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>中国工厂产能利用率回升，交付稳定性改善。</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>对美出口仍需应对关税，部分通过第三国转运与产品结构调整解决。</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>印证中国在配套完整度上的不可替代性，'China+1'演变为'China+1 但中国仍是主基地'。</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>行业性回流（结构性调整，非全面逆转）</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="W17" s="5" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>中高（路透社报道，中文媒体广泛转载；属趋势性报道，缺少单一企业完整数据）</t>
         </is>
       </c>
-      <c r="X17" s="5" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>行业级案例，建议与 RETURN_002 配合测试；NEWS_023（越南缺电）为其背景证据。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="51" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>RETURN_004</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>蜂巢能源 SVOLT（欧洲业务）</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EV Battery</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>36氪 / 财新网</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2024-10-28</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>https://www.caixin.com/2024-10-28/102250409.html</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Reconsideration / Return to China</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>电芯产能集中于中国，2020 年起规划德国萨尔州模组/PACK 工厂（24GWh）与勃兰登堡州电芯超级工厂。</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>中国为主，欧洲市场处于开拓期。</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>材料与设备来自中国。</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>欧洲电动车需求疲软、融资环境恶化，德国两座工厂建设资金不到位、进度一再延误。</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>cost_change</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>欧洲销售疲软 + 经济挑战 + 融资困难，海外扩张的投入产出不成立。</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>维持现有海外布局（收缩新增）</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建德国工厂、终止欧洲子公司运营（自 2025 年 1 月起关闭欧洲业务），资源集中于中国与泰国等已投产基地。</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Political Risk; Operational Risk</t>
         </is>
       </c>
-      <c r="Q18" s="5" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>停止约 300 亿元级别的海外投资计划，避免持续亏损。</t>
         </is>
       </c>
-      <c r="R18" s="5" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>欧洲产能归零，中国与泰国基地继续运营。</t>
         </is>
       </c>
-      <c r="S18" s="5" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>退出欧洲本地化生产，欧洲市场改以出口方式服务。</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>海外布局从'欧洲 + 东南亚'收缩为'东南亚'。</t>
         </is>
       </c>
-      <c r="U18" s="5" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>失败/主动退出（止损）</t>
         </is>
       </c>
-      <c r="V18" s="5" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="W18" s="5" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>高（财新、36氪等多家媒体报道一致）</t>
         </is>
       </c>
-      <c r="X18" s="5" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>与 RELOC_006（蜂巢泰国投产）构成同一公司内'一地成功、一地退出'的对照，非常适合 Scenario Simulation。</t>
         </is>
@@ -3317,9 +2683,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:X18"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="https://m.thepaper.cn/newsDetail_forward_20810032" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3331,7 +2694,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -3341,7 +2704,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>evidence_id</t>
@@ -4218,7 +3581,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -4226,353 +3589,353 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>取值</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>case_id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>案例唯一编号</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>企业名称</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>行业</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>来源媒体/文件</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>关键决策或事件日期</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>原文链接</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>case_type</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>案例类型（三类之一）</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>China → Southeast Asia relocation / China + 1 strategy / Reconsideration / Return to China</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>initial_production_layout</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>决策前：生产布局</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>initial_main_markets</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>决策前：主要市场</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>initial_supply_chain</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>决策前：供应链结构</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>initial_problem</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>决策前：面临的问题</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>decision_trigger</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>决策触发因素（6 类）</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>tariff_pressure / geopolitical_uncertainty / cost_change / supplier_issue / market_access / regulation_change</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>trigger_detail</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>触发因素说明</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>decision_type</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>实际决策分类（3 类）</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>多地区混合布局 / 维持现有海外布局 / 提高中国生产比例</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>actual_decision</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>实际决策内容</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>related_risk</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>相关风险（Task 1 口径）</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Trade Risk / Political Risk / Supply Chain Risk / Regulatory Risk / Market Access Risk / Operational Risk（可多选，; 分隔）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>outcome_cost_impact</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>结果：成本影响</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>outcome_production_performance</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>结果：生产表现</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>outcome_market_access</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>结果：市场准入</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>outcome_supply_chain_impact</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>结果：供应链影响</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>outcome_verdict</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>结果结论（成功/失败/待观察）</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>成功 / 失败 / 待观察（含主动退出与止损）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>related_evidence_ids</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>关联证据 ID</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>verification_status</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>真实性核验状态</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4586,7 +3949,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -4594,207 +3957,207 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>验收项</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>案例数量</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>17 个</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>要求 ≥10，最好 15 左右</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="51" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>案例类型覆盖</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>China + 1 strategy / China → Southeast Asia relocation / Reconsideration / Return to China</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>三类是否齐全</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>决策触发因素覆盖</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>cost_change / geopolitical_uncertainty / market_access / regulation_change / supplier_issue / tariff_pressure</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>决策类型覆盖</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>多地区混合布局 / 提高中国生产比例 / 维持现有海外布局（收缩新增）</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>三种决策分类是否齐全</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="101" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>行业覆盖</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Automotive (EV) / Battery Materials / EV Battery / EV Battery / Consumer Battery / EV Battery / Energy Storage / Electronics / Semiconductor / Electronics Manufacturing / General Manufacturing / Supply Chain / Solar Manufacturing</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>优先 EV Battery / Battery Materials / Automotive / Supply Chain / Electronics，其次 Semiconductor / Solar</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>背景→决策→结果链条</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>100% 完整</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>每个案例均有 Initial Situation / Decision / Outcome 三段</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>真实性核验</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>全部来自公开报道或公司公告</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>verification_status 逐条标注；两条为财经自媒体整理，需以年报核实</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>可追溯性</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>全部绑定 related_evidence_ids</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>共 26 条来源，见 Evidence Index</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>能否用于 Scenario Simulation</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>含 4 个'待观察/建设中'与 2 个'失败/退出'案例，可测试不确定与反向情景</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>未覆盖</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>'维持现有海外布局'由 RETURN_004 覆盖</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="51" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>已知局限</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1) 多数结果字段来自媒体转述，财务口径的成本影响未做量化；2) 4 个案例的最终结果尚未发生；3) 行业级案例 RETURN_003 缺少单一企业完整数据；4) related_risk 统一使用 Task 1 的六类风险词表（Cost Risk 已归并为 Operational Risk）。</t>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>1) 多数结果字段来自媒体转述，财务口径的成本影响未做量化；2) 4 个案例的最终结果尚未发生；3) 行业级案例 RETURN_003 缺少单一企业完整数据。</t>
         </is>
       </c>
     </row>

--- a/data/processed/case_database_v0.1.xlsx
+++ b/data/processed/case_database_v0.1.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Database'!$A$1:$X$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evidence Index'!$A$1:$F$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evidence Index'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1845,17 +1845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>ANTARA（印尼国家通讯社）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>在西爪哇省苏邦工业园区建设印尼工厂，总投资约 10 亿美元，规划年产能 15 万辆，计划 2025 年底前竣工；与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
+          <t>在西爪哇省苏邦 Smartpolitan 工业园区建设印尼工厂，投资约 16 万亿印尼盾（约 10 亿美元），最大年产能 15 万辆；2026-09-03 正式投产启用，为比亚迪全球第 13 座整车工厂。与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>本地生产规避印尼整车进口关税，获得电动车补贴资格。</t>
+          <t>本地生产规避印尼整车进口关税并满足本地化率（TKDN）要求，保住电动车激励资格；工厂投资约 16 万亿印尼盾。</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>截至 2025 年报道仍处于建设阶段，预计 2025 年底竣工（结果待验证）。</t>
+          <t>2026-09-03 正式投产，最大年产能 15 万辆，投产后实际产量约 1 万辆/月；启用仪式同场下线印尼本地生产的第 10 万辆整车。</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>以本地生产进入印尼市场，直接与日系品牌竞争。</t>
+          <t>2026-09 起停止整车进口、全面转为本地生产，以本地化进入印尼市场并与日系品牌竞争。</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>待观察（建设中）</t>
+          <t>成功（已投产并转为全本地生产）</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>中（来源为路透社转述的公司高管表态，竣工情况需以最新公告核实）</t>
+          <t>高（印尼国家通讯社 ANTARA 报道工厂投产、产能与停止整车进口）</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>与 RELOC_001 同属比亚迪，可对比同一企业不同市场的进入节奏。</t>
+          <t>与 RELOC_001 同属比亚迪。原 2025 年'预计年底竣工'的建设中表述已按 2026-09-03 投产事实更新。</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>计划在越南北部（太原省）投资约 40 亿美元建设芯片测试与封装工厂，分阶段实施；中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
+          <t>计划在越南北部（太原省）投资约 15 亿美元建设芯片测试与封装工厂（已见报道的初始项目）。媒体另称可能追加约 25 亿美元的第二工厂投资——该项为条件性后续计划，尚未确认实施，不能与初始项目合并为单一'约 40 亿美元'已确定项目。中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>截至 2026 年仍为投资计划阶段（结果待验证）。</t>
+          <t>截至 2026 年 10 月仍为投资计划阶段，未见公司正式公告确认实施或落地产能。</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>待观察（计划阶段）</t>
+          <t>待观察（计划阶段；投资金额需拆分核实）</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>中（多方媒体转述，未见公司正式公告）</t>
+          <t>中（媒体转述，未见公司正式公告；原新浪链接已失效，金额需以公司公告核实）</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>半导体行业'China+1'的代表，按任务优先级属第二梯队。</t>
+          <t>半导体行业'China+1'的对照案例，属第二梯队，非 EV/Battery 主线；已报道的约 15 亿美元初始项目与条件性的约 25 亿美元后续投资必须分开表述。</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2025 年 7 月及 12 月，富士康两度从印度工厂撤回中国大陆工程师与技术团队，部分产能与订单回流中国大陆；印度的组装布局并未取消，但节奏明显放缓。</t>
+          <t>2025 年 7 月及 12 月，富士康两度要求/撤回其印度工厂的中国大陆工程师与技术团队（彭博社等报道）。印度的组装布局并未取消，但推进节奏明显放缓。注：现有证据仅支持'工程团队撤回、工程支持减弱'，不足以证明订单或产能已实际回流中国。</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；中国基地继续承担高难度工序。</t>
+          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；高难度工序仍由中国基地承担。</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>印度工厂良率与产能爬坡受阻，中国大陆产能利用率回升。</t>
+          <t>印度工厂工程支持减弱、本地良率与产能爬坡受阻（有报道支持）；中国大陆产能利用率是否回升尚无直接证据，待验证。</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>验证了'关键工序与工程能力仍在中国'的结构性依赖。</t>
+          <t>印证了'关键工序与工程能力仍依赖中国'的结构性依赖（有报道支持）。</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>局部回流（未完全放弃印度）</t>
+          <t>工程团队撤回（订单/产能回流中国为待验证推断，未完全放弃印度）</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>中高（多家媒体一致，均引自知情人士）</t>
+          <t>中（工程团队撤回有彭博社等报道支持；'订单/产能回流中国'缺乏直接证据，不可作为既定事实）</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>最好与'订单回流中国'行业案例（RETURN_003）一起用于情景模拟。</t>
+          <t>保留'工程支持减弱 + 本地爬坡受阻'的已支持事实；'订单回流中国'如需保留须补直接证据。可与行业级 RETURN_003 配合做情景模拟。</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>链接已核验</t>
+          <t>原链接已失效（页面不存在），待替换来源；金额口径待核实</t>
         </is>
       </c>
     </row>
@@ -3568,8 +3568,72 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NEWS_024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ANTARA（印尼国家通讯社）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pabrik BYD di Subang resmi beroperasi dan serap 5.000 pekerja lokal（比亚迪苏邦工厂正式投产，吸纳 5000 名本地员工）</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>链接已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NEWS_025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ANTARA（印尼国家通讯社）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BYD setop impor mobil ke Indonesia, beralih penuh ke produksi lokal（比亚迪停止整车进口，全面转向本地生产）</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5724855/byd-setop-impor-mobil-ke-indonesia-beralih-penuh-ke-produksi-lokal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>链接已核验</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F27"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4105,7 +4169,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>共 26 条来源，见 Evidence Index</t>
+          <t>共 28 条来源，见 Evidence Index</t>
         </is>
       </c>
     </row>

--- a/data/processed/case_database_v0.1.xlsx
+++ b/data/processed/case_database_v0.1.xlsx
@@ -13,7 +13,7 @@
     <sheet name="QA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Database'!$A$1:$X$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Database'!$A$1:$Z$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evidence Index'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,9 +484,11 @@
     <col width="36" customWidth="1" min="19" max="19"/>
     <col width="40" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="26" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="54" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="44" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -602,10 +604,20 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>external_source_refs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>related_evidence_rationale</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>verification_status</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -719,15 +731,25 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>R1 美国对华电动车关税/欧盟反补贴(EU_003)是出海触发；R3 中美自泰进口整车与电池数据(TRD_001)显示泰国通道；R4 光模块厂泰国产能(CASE_004)提供同去向类比；R3 全球EV格局(IEA_001)；R2 泰国物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>高（官方发布 + 多家主流媒体一致）</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>整车厂跟随关税出海的标准案例，可作为 Scenario Simulation 的基准情景。</t>
         </is>
@@ -841,15 +863,25 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>R1 关税与泰国本地化要求为触发；R2 美国自泰进口整车/电池(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>高（公司互动平台确认 + 媒体报道）</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>与比亚迪泰国案例对照，可用于比较不同车企的东南亚本地化路径。</t>
         </is>
@@ -963,15 +995,25 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口电池数据(TRD_001)与中国对越中间品出口(TRD_003)共同刻画越南通道；R3 中国电池厂全球份额(SNE_001)；R2 物流绩效(WB_001)；R4 东南亚建厂类比(CASE_007)</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>中高（开工有明确报道；2026 年投产状态来自公司互动平台转述）</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1081,15 +1123,25 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自马进口电池(TRD_001)+中国对马中间品出口(TRD_003)；R4 马来西亚工厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>高（公司发布 + 主流财经媒体）</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>可用于比较'东南亚出口枢纽'与'近岸（墨西哥/匈牙利）'两种路径。</t>
         </is>
@@ -1203,15 +1255,25 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口(TRD_001)+对越中间品出口(TRD_003)；R4 东南亚建厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>中高（公告明确；投产时间来自公司投资者关系记录转述）</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>少见的'结果尚未发生'案例，可用于测试模型对不确定结论的处理。</t>
         </is>
@@ -1325,15 +1387,25 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟反补贴税(EU_003)抬高欧洲出口成本；R2 美国自泰进口(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>高（多家媒体一致）</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>与 RETURN_004（蜂巢停建德国工厂）同一公司，可直接对比'东南亚收缩 vs 欧洲退出'的策略差异。</t>
         </is>
@@ -1447,15 +1519,25 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼贸易政策审议包含镍下游化政策(WTO_004)；R1 中国对印尼中间品出口(TRD_003)；R3 电池材料格局(SNE_001)；R2 印尼物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>高（公司公告 + 主流财经媒体）</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>典型的'资源端外移而非制造端外移'案例。</t>
         </is>
@@ -1569,15 +1651,25 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化与本地化要求(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>高（公司披露 + 媒体报道）</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>与华友钴业对照，可用于'资源国集中度'风险讨论。</t>
         </is>
@@ -1691,15 +1783,25 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)+CRMA(EU_002)构成匈牙利建厂的合规与准入约束；R3 宁德时代全球份额(SNE_001)与EV格局(IEA_001)</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>中高（2026 年节点高质量来源；2022 年投资额来自媒体转述）</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>'欧洲本地化'路径的代表案例，与东南亚路径形成对照。</t>
         </is>
@@ -1813,15 +1915,25 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化/本地化(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 份额与格局(SNE_001,IEA_001)</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>中高（公司发布 + 多家媒体，含彭博社转述）</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>可用于讨论'资源国要求本地化'这一触发因素。</t>
         </is>
@@ -1935,15 +2047,25 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼本地化政策(WTO_004)直接对应'转为全本地生产'的结果；R3 格局(IEA_001,SNE_001)；R1 中间品出口(TRD_003)+欧盟反补贴(EU_003)说明多地区布局动因</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>高（印尼国家通讯社 ANTARA 报道工厂投产、产能与停止整车进口）</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>与 RELOC_001 同属比亚迪。原 2025 年'预计年底竣工'的建设中表述已按 2026-09-03 投产事实更新。</t>
         </is>
@@ -2057,15 +2179,25 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>R1 美国对东南亚四国光伏反规避终裁(DOC_001)是该案例决策的直接触发；R4 同调查'已规避/未规避'案例(CASE_002,CASE_003)；R2 美国光伏进口数据(TRD_002)</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>中（来源为财经自媒体对公开产能布局的整理，需以公司年报/官网核实）</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>与 Task 1 的光伏反规避证据（CASE_002/CASE_003/DOC_001）直接呼应，可用于跨任务串联。</t>
         </is>
@@ -2179,15 +2311,25 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD 投资报告把三星/富士康类外迁作为 FDI 案例(UNCTAD_001)；R1 对越中间品出口(TRD_003)；R2 越南物流绩效(WB_001)；R3 IMF 对水平型 FDI 的举例(IMF_001)</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>中（媒体转述，未见公司正式公告；原新浪链接已失效，金额需以公司公告核实）</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>半导体行业'China+1'的对照案例，属第二梯队，非 EV/Battery 主线；已报道的约 15 亿美元初始项目与条件性的约 25 亿美元后续投资必须分开表述。</t>
         </is>
@@ -2301,15 +2443,25 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>R4 大旺金属'订单转移后回流'案例(CASE_001)是直接类比；R1 对马中间品出口与配套依赖(TRD_003)；R2 物流成本(WB_001)；R3 行业格局(SNE_001)</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>高（上市公司公告，多家财经媒体一致）</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>完整的'规划→终止'闭环案例，最能体现 Return/Reconsideration 类型。</t>
         </is>
@@ -2423,15 +2575,25 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD_001 直接引用路透'富士康印度 iPhone 出口'报道（同源提示）；R2 印度贸易政策审议与关税(WTO_002,WTO_003)；R4 回流类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>中（工程团队撤回有彭博社等报道支持；'订单/产能回流中国'缺乏直接证据，不可作为既定事实）</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>保留'工程支持减弱 + 本地爬坡受阻'的已支持事实；'订单回流中国'如需保留须补直接证据。可与行业级 RETURN_003 配合做情景模拟。</t>
         </is>
@@ -2545,15 +2707,25 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>R4 行业层面回流的核心类比是 CASE_001（大旺金属，订单外移印度后回流）；R2 物流与配套成本(WB_001)；R1 关税背景(TRD_001)；R3 美国供应链调查(KPMG_001)</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>中高（路透社报道，中文媒体广泛转载；属趋势性报道，缺少单一企业完整数据）</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>行业级案例，建议与 RETURN_002 配合测试；NEWS_023（越南缺电）为其背景证据。</t>
         </is>
@@ -2667,22 +2839,32 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)是收缩欧洲布局的直接约束；R4 回流/收缩类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>高（财新、36氪等多家媒体报道一致）</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>与 RELOC_006（蜂巢泰国投产）构成同一公司内'一地成功、一地退出'的对照，非常适合 Scenario Simulation。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X18"/>
+  <autoFilter ref="A1:Z18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2693,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2702,6 +2884,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2735,6 +2918,11 @@
           <t>url_status</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>used_by_cases</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2767,6 +2955,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2799,6 +2992,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2831,6 +3029,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2863,6 +3066,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2895,6 +3103,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2927,6 +3140,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2959,6 +3177,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2991,6 +3214,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3023,6 +3251,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3055,6 +3288,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3087,6 +3325,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3119,6 +3362,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3151,6 +3399,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3183,6 +3436,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3215,6 +3473,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3247,6 +3510,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3279,6 +3547,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3311,6 +3584,11 @@
           <t>原链接已失效（页面不存在），待替换来源；金额口径待核实</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3343,6 +3621,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3375,6 +3658,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3407,6 +3695,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3439,6 +3732,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3471,6 +3769,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3503,6 +3806,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3535,6 +3843,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3567,6 +3880,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3599,6 +3917,11 @@
           <t>链接已核验</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3629,6 +3952,11 @@
       <c r="F29" t="inlineStr">
         <is>
           <t>链接已核验</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3970,7 +4298,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>关联证据 ID</t>
+          <t>关联证据 ID（Task 1 证据库，49 条内）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
@@ -3978,12 +4306,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>verification_status</t>
+          <t>external_source_refs</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>真实性核验状态</t>
+          <t>外部来源编号（新闻报道，见 Evidence Index）</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
@@ -3991,15 +4319,41 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>related_evidence_rationale</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>绑定依据（R1触发/R2目的地/R3行业/R4类比）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>verification_status</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>真实性核验状态</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4012,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4159,67 +4513,208 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>可追溯性</t>
+          <t>可追溯性（外部来源）</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>全部绑定 related_evidence_ids</t>
+          <t>28 条新闻/公告，编号见 Evidence Index</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>共 28 条来源，见 Evidence Index</t>
+          <t>external_source_refs 指向 Evidence Index，含 outlet/标题/日期/URL 与 used_by_cases</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>能否用于 Scenario Simulation</t>
+          <t>可追溯性（证据库绑定）</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>17/17 全部解析到 Task 1 的 49 条证据</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>含 4 个'待观察/建设中'与 2 个'失败/退出'案例，可测试不确定与反向情景</t>
+          <t>related_evidence_ids 已由外部新闻编号改为证据库内真实 ID；每条附绑定依据（R1触发/R2目的地/R3行业/R4类比）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>未覆盖</t>
+          <t>证据库链路校验</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>'维持现有海外布局'由 RETURN_004 覆盖</t>
+          <t>逐个 ID 与 evidence_metadata_v0.1.json 比对，无悬空引用</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>能否用于 Scenario Simulation</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>含 4 个'待观察/建设中'与 2 个'失败/退出'案例，可测试不确定与反向情景</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>'维持现有海外布局'由 RETURN_004 覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>held-out 校验</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>RAG 语料 49 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>语料泄漏检查（逐字）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>backend/scripts/check_case_leakage.py：17/17 通过，最高逐字重合 1.0%（10 字滑窗，阈值 5%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>隔离校验复跑</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>.venv/bin/python backend/scripts/check_case_leakage.py</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>退出码 0 = 案例 ID 不撞 / 来源 URL 不撞 / 无逐字重合 / related_evidence_ids 全部可解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>语料背景重合（已登记）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>4 处</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>RELOC_001/PLUS1_003 经 IEA_001 的 OEM 名单；PLUS1_004 经 DOC_001 的光伏反规避语境；PLUS1_005 经 IMF_001 的 FDI 举例；RETURN_002 经 UNCTAD_001 的路透引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>同源提示</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>其外部来源为路透报道，而语料 UNCTAD_001 引用了同一系列路透稿；属背景级同源，评测时需知悉</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>通用吸引子</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>CASE_001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>语料 CASE_001（大旺金属回流）出现在全部 17 个案例的 Top-5，是 Task 6 false positive 的来源之一，与 RETURN_003 构成同现象不同主体</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>已知局限</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>1) 多数结果字段来自媒体转述，财务口径的成本影响未做量化；2) 4 个案例的最终结果尚未发生；3) 行业级案例 RETURN_003 缺少单一企业完整数据。</t>
         </is>

--- a/data/processed/case_database_v0.1.xlsx
+++ b/data/processed/case_database_v0.1.xlsx
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>关联证据 ID（Task 1 证据库，49 条内）</t>
+          <t>关联证据 ID（Task 1 证据库，53 条内）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>17/17 全部解析到 Task 1 的 49 条证据</t>
+          <t>17/17 全部解析到 Task 1 的 53 条证据</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>RAG 语料 49 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
+          <t>RAG 语料 53 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>语料 CASE_001（大旺金属回流）出现在全部 17 个案例的 Top-5，是 Task 6 false positive 的来源之一，与 RETURN_003 构成同现象不同主体</t>
+          <t>语料 CASE_001（大旺金属回流）在 13/17（基线）/ 16/17（优化层）个案例的 Top-5 出现（v0.9.2 语料复测），是 Task 6 false positive 的来源之一，与 RETURN_003 构成同现象不同主体</t>
         </is>
       </c>
     </row>
